--- a/Практика1.xlsx
+++ b/Практика1.xlsx
@@ -129,9 +129,6 @@
     <t>Проверка работы клавиши "-" для уменьшения масштаба</t>
   </si>
   <si>
-    <t>Проверка работы клавиши "+" для уменьшения масштаба</t>
-  </si>
-  <si>
     <t>Failed</t>
   </si>
   <si>
@@ -154,6 +151,9 @@
   </si>
   <si>
     <t>1. Перейти в адресную строку              2. Изменить число в конце на меньшее</t>
+  </si>
+  <si>
+    <t>Проверка работы клавиши "+" для увеличения масштаба</t>
   </si>
 </sst>
 </file>
@@ -501,7 +501,7 @@
     <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,7 +600,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
@@ -627,7 +627,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>19</v>
@@ -654,19 +654,19 @@
         <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -675,25 +675,25 @@
         <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -702,13 +702,13 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>13</v>
